--- a/xlsx/Power/p2.xlsx
+++ b/xlsx/Power/p2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CD3C5F-2C9A-4D9C-9377-B7A5E162B0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867CE355-CD26-4DD0-B7EF-F86E89D4C353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD2D91D9-EEC8-4300-A422-DE123EEEB20F}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD2D91D9-EEC8-4300-A422-DE123EEEB20F}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.34200000000000003</v>
       </c>
       <c r="C1">
-        <v>0.46300000000000002</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="D1">
-        <v>0.56699999999999995</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="E1">
-        <v>0.628</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="F1">
-        <v>0.72599999999999998</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="G1">
-        <v>0.752</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="H1">
-        <v>0.78700000000000003</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="I1">
-        <v>0.82499999999999996</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="J1">
-        <v>0.88400000000000001</v>
+        <v>0.83299999999999996</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.38900000000000001</v>
       </c>
       <c r="C2">
-        <v>0.52</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="D2">
-        <v>0.63300000000000001</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="E2">
-        <v>0.69499999999999995</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="F2">
-        <v>0.77800000000000002</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="G2">
-        <v>0.80600000000000005</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="H2">
-        <v>0.84499999999999997</v>
+        <v>0.76400000000000001</v>
       </c>
       <c r="I2">
-        <v>0.85</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="J2">
-        <v>0.91200000000000003</v>
+        <v>0.86799999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,19 +468,19 @@
         <v>0.33</v>
       </c>
       <c r="C3">
-        <v>0.435</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="D3">
-        <v>0.52500000000000002</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="E3">
-        <v>0.58799999999999997</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="F3">
-        <v>0.69199999999999995</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="G3">
-        <v>0.73</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="H3">
         <v>0.76500000000000001</v>
@@ -489,39 +489,39 @@
         <v>0.78600000000000003</v>
       </c>
       <c r="J3">
-        <v>0.84499999999999997</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.17699999999999999</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="B4">
-        <v>0.30399999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="C4">
-        <v>0.40400000000000003</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="D4">
-        <v>0.48399999999999999</v>
+        <v>0.48299999999999998</v>
       </c>
       <c r="E4">
         <v>0.56499999999999995</v>
       </c>
       <c r="F4">
-        <v>0.65400000000000003</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="G4">
-        <v>0.70699999999999996</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="H4">
-        <v>0.73699999999999999</v>
+        <v>0.73599999999999999</v>
       </c>
       <c r="I4">
         <v>0.755</v>
       </c>
       <c r="J4">
-        <v>0.82299999999999995</v>
+        <v>0.82399999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="C5">
-        <v>7.3999999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>8.7999999999999995E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E5">
-        <v>8.5999999999999993E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="F5">
-        <v>8.5999999999999993E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G5">
-        <v>9.2999999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="H5">
-        <v>0.09</v>
+        <v>3.9E-2</v>
       </c>
       <c r="I5">
-        <v>0.113</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="J5">
-        <v>0.10100000000000001</v>
+        <v>4.8000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="C6">
-        <v>0.52300000000000002</v>
+        <v>0.621</v>
       </c>
       <c r="D6">
-        <v>0.63800000000000001</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="E6">
-        <v>0.7</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="F6">
-        <v>0.78400000000000003</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="G6">
-        <v>0.81799999999999995</v>
+        <v>0.82</v>
       </c>
       <c r="H6">
-        <v>0.84599999999999997</v>
+        <v>0.84699999999999998</v>
       </c>
       <c r="I6">
-        <v>0.86</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="J6">
-        <v>0.90700000000000003</v>
+        <v>0.91300000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,25 +596,25 @@
         <v>0.377</v>
       </c>
       <c r="C7">
-        <v>0.48399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="D7">
         <v>0.59599999999999997</v>
       </c>
       <c r="E7">
-        <v>0.64400000000000002</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="F7">
-        <v>0.73499999999999999</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="G7">
-        <v>0.76600000000000001</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="H7">
         <v>0.80300000000000005</v>
       </c>
       <c r="I7">
-        <v>0.81499999999999995</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="J7">
         <v>0.88100000000000001</v>
@@ -628,28 +628,28 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="C8">
-        <v>0.249</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="D8">
-        <v>0.33300000000000002</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="E8">
-        <v>0.39</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F8">
-        <v>0.47799999999999998</v>
+        <v>0.318</v>
       </c>
       <c r="G8">
-        <v>0.51100000000000001</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="H8">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="I8">
-        <v>0.60599999999999998</v>
+        <v>0.32</v>
       </c>
       <c r="J8">
-        <v>0.65</v>
+        <v>0.34799999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="C9">
-        <v>0.42299999999999999</v>
+        <v>0.67800000000000005</v>
       </c>
       <c r="D9">
-        <v>0.30499999999999999</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="E9">
-        <v>0.28100000000000003</v>
+        <v>0.71899999999999997</v>
       </c>
       <c r="F9">
-        <v>0.313</v>
+        <v>0.443</v>
       </c>
       <c r="G9">
-        <v>0.35199999999999998</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="H9">
-        <v>0.34300000000000003</v>
+        <v>0.39</v>
       </c>
       <c r="I9">
-        <v>0.373</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="J9">
-        <v>0.40699999999999997</v>
+        <v>0.432</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p2.xlsx
+++ b/xlsx/Power/p2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867CE355-CD26-4DD0-B7EF-F86E89D4C353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F83F843-6CB6-4CD8-8957-709B8DB70B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD2D91D9-EEC8-4300-A422-DE123EEEB20F}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD2D91D9-EEC8-4300-A422-DE123EEEB20F}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,34 +398,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="B1">
         <v>0.34200000000000003</v>
       </c>
       <c r="C1">
-        <v>0.18099999999999999</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="D1">
-        <v>0.34100000000000003</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="E1">
-        <v>0.46400000000000002</v>
+        <v>0.628</v>
       </c>
       <c r="F1">
-        <v>0.59599999999999997</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="G1">
-        <v>0.66100000000000003</v>
+        <v>0.752</v>
       </c>
       <c r="H1">
-        <v>0.71599999999999997</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="I1">
-        <v>0.75800000000000001</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="J1">
-        <v>0.83299999999999996</v>
+        <v>0.88400000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.38900000000000001</v>
       </c>
       <c r="C2">
-        <v>0.21199999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="D2">
-        <v>0.39600000000000002</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="E2">
-        <v>0.52100000000000002</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="F2">
-        <v>0.66700000000000004</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="G2">
-        <v>0.71299999999999997</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="H2">
-        <v>0.76400000000000001</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="I2">
-        <v>0.79900000000000004</v>
+        <v>0.85</v>
       </c>
       <c r="J2">
-        <v>0.86799999999999999</v>
+        <v>0.91200000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,19 +468,19 @@
         <v>0.33</v>
       </c>
       <c r="C3">
-        <v>0.47699999999999998</v>
+        <v>0.435</v>
       </c>
       <c r="D3">
-        <v>0.53300000000000003</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="E3">
-        <v>0.59499999999999997</v>
+        <v>0.58799999999999997</v>
       </c>
       <c r="F3">
-        <v>0.69799999999999995</v>
+        <v>0.69199999999999995</v>
       </c>
       <c r="G3">
-        <v>0.73099999999999998</v>
+        <v>0.73</v>
       </c>
       <c r="H3">
         <v>0.76500000000000001</v>
@@ -489,39 +489,39 @@
         <v>0.78600000000000003</v>
       </c>
       <c r="J3">
-        <v>0.85</v>
+        <v>0.84499999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.19600000000000001</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="B4">
-        <v>0.315</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="C4">
-        <v>0.41099999999999998</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="D4">
-        <v>0.48299999999999998</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="E4">
         <v>0.56499999999999995</v>
       </c>
       <c r="F4">
-        <v>0.65500000000000003</v>
+        <v>0.65400000000000003</v>
       </c>
       <c r="G4">
-        <v>0.70599999999999996</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="H4">
-        <v>0.73599999999999999</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="I4">
         <v>0.755</v>
       </c>
       <c r="J4">
-        <v>0.82399999999999995</v>
+        <v>0.82299999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="D5">
-        <v>6.0000000000000001E-3</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E5">
-        <v>6.0000000000000001E-3</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="F5">
-        <v>1.7000000000000001E-2</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="G5">
-        <v>2.9000000000000001E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="H5">
-        <v>3.9E-2</v>
+        <v>0.09</v>
       </c>
       <c r="I5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.113</v>
       </c>
       <c r="J5">
-        <v>4.8000000000000001E-2</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="C6">
-        <v>0.621</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="D6">
-        <v>0.66500000000000004</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="E6">
-        <v>0.72199999999999998</v>
+        <v>0.7</v>
       </c>
       <c r="F6">
-        <v>0.79400000000000004</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="G6">
-        <v>0.82</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="H6">
-        <v>0.84699999999999998</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="I6">
-        <v>0.86499999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="J6">
-        <v>0.91300000000000003</v>
+        <v>0.90700000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,25 +596,25 @@
         <v>0.377</v>
       </c>
       <c r="C7">
-        <v>0.48</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="D7">
         <v>0.59599999999999997</v>
       </c>
       <c r="E7">
-        <v>0.64500000000000002</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="F7">
-        <v>0.73399999999999999</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="G7">
-        <v>0.76300000000000001</v>
+        <v>0.76600000000000001</v>
       </c>
       <c r="H7">
         <v>0.80300000000000005</v>
       </c>
       <c r="I7">
-        <v>0.81299999999999994</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="J7">
         <v>0.88100000000000001</v>
@@ -628,28 +628,28 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="C8">
-        <v>1.7999999999999999E-2</v>
+        <v>0.249</v>
       </c>
       <c r="D8">
-        <v>0.13500000000000001</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="E8">
-        <v>0.23100000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="F8">
-        <v>0.318</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="G8">
-        <v>0.39200000000000002</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="H8">
-        <v>0.45</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I8">
-        <v>0.32</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="J8">
-        <v>0.34799999999999998</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -657,31 +657,31 @@
         <v>0.127</v>
       </c>
       <c r="B9">
-        <v>0.16300000000000001</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="C9">
-        <v>0.67800000000000005</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="D9">
-        <v>0.92200000000000004</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="E9">
-        <v>0.71899999999999997</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="F9">
-        <v>0.443</v>
+        <v>0.313</v>
       </c>
       <c r="G9">
-        <v>0.41699999999999998</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="H9">
-        <v>0.39</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="I9">
-        <v>0.39900000000000002</v>
+        <v>0.373</v>
       </c>
       <c r="J9">
-        <v>0.432</v>
+        <v>0.40699999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p2.xlsx
+++ b/xlsx/Power/p2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F83F843-6CB6-4CD8-8957-709B8DB70B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED14E147-232B-4853-BAFB-AFA7C284EDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD2D91D9-EEC8-4300-A422-DE123EEEB20F}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD2D91D9-EEC8-4300-A422-DE123EEEB20F}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000_ ;[Red]\-0.000\ "/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -68,8 +71,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -393,12 +397,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B37DE5F3-A4CB-425B-B342-175540580921}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.183</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="B1">
         <v>0.34200000000000003</v>
@@ -407,13 +411,13 @@
         <v>0.46300000000000002</v>
       </c>
       <c r="D1">
-        <v>0.56699999999999995</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="E1">
-        <v>0.628</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="F1">
-        <v>0.72599999999999998</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="G1">
         <v>0.752</v>
@@ -422,184 +426,238 @@
         <v>0.78700000000000003</v>
       </c>
       <c r="I1">
-        <v>0.82499999999999996</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="J1">
-        <v>0.88400000000000001</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.20300000000000001</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="B2">
-        <v>0.38900000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="C2">
         <v>0.52</v>
       </c>
       <c r="D2">
-        <v>0.63300000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="E2">
-        <v>0.69499999999999995</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="F2">
-        <v>0.77800000000000002</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="G2">
         <v>0.80600000000000005</v>
       </c>
       <c r="H2">
-        <v>0.84499999999999997</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="I2">
-        <v>0.85</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="J2">
-        <v>0.91200000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="B3">
         <v>0.33</v>
       </c>
       <c r="C3">
-        <v>0.435</v>
+        <v>0.438</v>
       </c>
       <c r="D3">
-        <v>0.52500000000000002</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="E3">
-        <v>0.58799999999999997</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="F3">
-        <v>0.69199999999999995</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="G3">
-        <v>0.73</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="H3">
-        <v>0.76500000000000001</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="I3">
-        <v>0.78600000000000003</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="J3">
-        <v>0.84499999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.17699999999999999</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="B4">
-        <v>0.30399999999999999</v>
+        <v>0.308</v>
       </c>
       <c r="C4">
-        <v>0.40400000000000003</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="D4">
-        <v>0.48399999999999999</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="E4">
-        <v>0.56499999999999995</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="F4">
-        <v>0.65400000000000003</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="G4">
-        <v>0.70699999999999996</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="H4">
         <v>0.73699999999999999</v>
       </c>
       <c r="I4">
-        <v>0.755</v>
+        <v>0.76600000000000001</v>
       </c>
       <c r="J4">
-        <v>0.82299999999999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>7.4999999999999997E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="B5">
-        <v>6.0999999999999999E-2</v>
+        <v>2.7E-2</v>
       </c>
       <c r="C5">
-        <v>7.3999999999999996E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="D5">
-        <v>8.7999999999999995E-2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="E5">
-        <v>8.5999999999999993E-2</v>
+        <v>0.114</v>
       </c>
       <c r="F5">
-        <v>8.5999999999999993E-2</v>
+        <v>0.126</v>
       </c>
       <c r="G5">
-        <v>9.2999999999999999E-2</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="H5">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="I5">
-        <v>0.113</v>
+        <v>0.21</v>
       </c>
       <c r="J5">
-        <v>0.10100000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.21199999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="B6">
         <v>0.39500000000000002</v>
       </c>
       <c r="C6">
-        <v>0.52300000000000002</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="D6">
-        <v>0.63800000000000001</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="E6">
-        <v>0.7</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="F6">
-        <v>0.78400000000000003</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="G6">
-        <v>0.81799999999999995</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="H6">
-        <v>0.84599999999999997</v>
+        <v>0.84</v>
       </c>
       <c r="I6">
-        <v>0.86</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="J6">
-        <v>0.90700000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.20799999999999999</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="B7">
-        <v>0.377</v>
+        <v>0.375</v>
       </c>
       <c r="C7">
-        <v>0.48399999999999999</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="D7">
-        <v>0.59599999999999997</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="E7">
         <v>0.64400000000000002</v>
@@ -619,10 +677,19 @@
       <c r="J7">
         <v>0.88100000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9.4E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="B8">
         <v>0.17299999999999999</v>
@@ -631,58 +698,197 @@
         <v>0.249</v>
       </c>
       <c r="D8">
-        <v>0.33300000000000002</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="E8">
-        <v>0.39</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="F8">
-        <v>0.47799999999999998</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="G8">
         <v>0.51100000000000001</v>
       </c>
       <c r="H8">
-        <v>0.55000000000000004</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="I8">
         <v>0.60599999999999998</v>
       </c>
       <c r="J8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.127</v>
       </c>
       <c r="B9">
-        <v>0.16200000000000001</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="C9">
-        <v>0.42299999999999999</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="D9">
-        <v>0.30499999999999999</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="E9">
-        <v>0.28100000000000003</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="F9">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="G9">
-        <v>0.35199999999999998</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="H9">
-        <v>0.34300000000000003</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="I9">
-        <v>0.373</v>
+        <v>0.377</v>
       </c>
       <c r="J9">
-        <v>0.40699999999999997</v>
-      </c>
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+    </row>
+    <row r="19" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="13:21" x14ac:dyDescent="0.25">
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
